--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294937190" windowHeight="13140"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21825" windowHeight="9945"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -21,94 +21,94 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제의 세계에 접속했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
   </x:si>
   <x:si>
-    <x:t>다만 아직 야근이 남아 있습니다. 좀 더 고생해주세요.</x:t>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 대답하지 않는다,대답한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
   </x:si>
   <x:si>
     <x:t>Texture2D/Texture2D_Loading_1</x:t>
   </x:si>
   <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 대답하지 않는다,대답한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 세계에 접속 하셨습니다…&lt;np&gt;오랜시간 기다리셨는데..&lt;np&gt;제가 많이 늦었군요...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용사님이시어..고생하셨군요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
+    <x:t>SelectionDialogueIdList</x:t>
   </x:si>
   <x:si>
     <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -198,16 +198,16 @@
   <x:borders count="2">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -230,7 +230,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="13">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -271,8 +274,406 @@
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="0"/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
+          <x:bgColor rgb="ffaebfea"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
 </x:styleSheet>
 </file>
 
@@ -472,561 +873,559 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:R35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <x:col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <x:col min="3" max="6" width="77.08984375" customWidth="1"/>
-    <x:col min="7" max="8" width="50.7265625" customWidth="1"/>
+    <x:col min="1" max="1" width="26.36328125" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
+    <x:col min="3" max="6" width="77.08984375" style="1" customWidth="1"/>
+    <x:col min="7" max="8" width="50.7265625" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A4" s="5" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G4" s="5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H4" s="5"/>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+      <x:c r="L4" s="4"/>
+      <x:c r="M4" s="4"/>
+      <x:c r="N4" s="4"/>
+      <x:c r="O4" s="4"/>
+      <x:c r="P4" s="4"/>
+      <x:c r="Q4" s="4"/>
+      <x:c r="R4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A5" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="6"/>
+      <x:c r="C5" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E5" s="5"/>
+      <x:c r="F5" s="5"/>
+      <x:c r="G5" s="5"/>
+      <x:c r="H5" s="5"/>
+      <x:c r="I5" s="4"/>
+      <x:c r="J5" s="4"/>
+      <x:c r="K5" s="4"/>
+      <x:c r="L5" s="4"/>
+      <x:c r="M5" s="4"/>
+      <x:c r="N5" s="4"/>
+      <x:c r="O5" s="4"/>
+      <x:c r="P5" s="4"/>
+      <x:c r="Q5" s="4"/>
+      <x:c r="R5" s="4"/>
+    </x:row>
+    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A6" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
+      <x:c r="F6" s="5"/>
+      <x:c r="G6" s="5"/>
+      <x:c r="H6" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4"/>
+      <x:c r="L6" s="4"/>
+      <x:c r="M6" s="4"/>
+      <x:c r="N6" s="4"/>
+      <x:c r="O6" s="4"/>
+      <x:c r="P6" s="4"/>
+      <x:c r="Q6" s="4"/>
+      <x:c r="R6" s="4"/>
+    </x:row>
+    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B7" s="5"/>
+      <x:c r="C7" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D7" s="5"/>
+      <x:c r="E7" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G7" s="5"/>
+      <x:c r="H7" s="5"/>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
+      <x:c r="K7" s="4"/>
+      <x:c r="L7" s="4"/>
+      <x:c r="M7" s="4"/>
+      <x:c r="N7" s="4"/>
+      <x:c r="O7" s="4"/>
+      <x:c r="P7" s="4"/>
+      <x:c r="Q7" s="4"/>
+      <x:c r="R7" s="4"/>
+    </x:row>
+    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B8" s="7"/>
+      <x:c r="C8" s="7" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="D8" s="7"/>
+      <x:c r="E8" s="7"/>
+      <x:c r="F8" s="7"/>
+      <x:c r="G8" s="7"/>
+      <x:c r="H8" s="7"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
+      <x:c r="L8" s="4"/>
+      <x:c r="M8" s="4"/>
+      <x:c r="N8" s="4"/>
+      <x:c r="O8" s="4"/>
+      <x:c r="P8" s="4"/>
+      <x:c r="Q8" s="4"/>
+      <x:c r="R8" s="4"/>
+    </x:row>
+    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B9" s="7"/>
+      <x:c r="C9" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D9" s="7"/>
+      <x:c r="E9" s="7"/>
+      <x:c r="F9" s="7"/>
+      <x:c r="G9" s="7"/>
+      <x:c r="H9" s="5" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="4"/>
+      <x:c r="K9" s="4"/>
+      <x:c r="L9" s="4"/>
+      <x:c r="M9" s="4"/>
+      <x:c r="N9" s="4"/>
+      <x:c r="O9" s="4"/>
+      <x:c r="P9" s="4"/>
+      <x:c r="Q9" s="4"/>
+      <x:c r="R9" s="4"/>
+    </x:row>
+    <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A10" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B10" s="8"/>
+      <x:c r="C10" s="8" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H3" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B4" s="5"/>
-      <x:c r="C4" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="3"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3"/>
-      <x:c r="L4" s="3"/>
-      <x:c r="M4" s="3"/>
-      <x:c r="N4" s="3"/>
-      <x:c r="O4" s="3"/>
-      <x:c r="P4" s="3"/>
-      <x:c r="Q4" s="3"/>
-      <x:c r="R4" s="3"/>
-    </x:row>
-    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B5" s="5"/>
-      <x:c r="C5" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E5" s="4"/>
-      <x:c r="F5" s="4"/>
-      <x:c r="G5" s="4"/>
-      <x:c r="H5" s="4"/>
-      <x:c r="I5" s="3"/>
-      <x:c r="J5" s="3"/>
-      <x:c r="K5" s="3"/>
-      <x:c r="L5" s="3"/>
-      <x:c r="M5" s="3"/>
-      <x:c r="N5" s="3"/>
-      <x:c r="O5" s="3"/>
-      <x:c r="P5" s="3"/>
-      <x:c r="Q5" s="3"/>
-      <x:c r="R5" s="3"/>
-    </x:row>
-    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A6" s="4" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B6" s="5"/>
-      <x:c r="C6" s="4" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="4"/>
-      <x:c r="E6" s="4"/>
-      <x:c r="F6" s="4"/>
-      <x:c r="G6" s="4"/>
-      <x:c r="H6" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
-      <x:c r="K6" s="3"/>
-      <x:c r="L6" s="3"/>
-      <x:c r="M6" s="3"/>
-      <x:c r="N6" s="3"/>
-      <x:c r="O6" s="3"/>
-      <x:c r="P6" s="3"/>
-      <x:c r="Q6" s="3"/>
-      <x:c r="R6" s="3"/>
-    </x:row>
-    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="4"/>
-      <x:c r="E7" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G7" s="4"/>
-      <x:c r="H7" s="4"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
-      <x:c r="L7" s="3"/>
-      <x:c r="M7" s="3"/>
-      <x:c r="N7" s="3"/>
-      <x:c r="O7" s="3"/>
-      <x:c r="P7" s="3"/>
-      <x:c r="Q7" s="3"/>
-      <x:c r="R7" s="3"/>
-    </x:row>
-    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A8" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D8" s="6"/>
-      <x:c r="E8" s="6"/>
-      <x:c r="F8" s="6"/>
-      <x:c r="G8" s="6"/>
-      <x:c r="H8" s="6"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
-      <x:c r="L8" s="3"/>
-      <x:c r="M8" s="3"/>
-      <x:c r="N8" s="3"/>
-      <x:c r="O8" s="3"/>
-      <x:c r="P8" s="3"/>
-      <x:c r="Q8" s="3"/>
-      <x:c r="R8" s="3"/>
-    </x:row>
-    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A9" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="6"/>
-      <x:c r="E9" s="6"/>
-      <x:c r="F9" s="6"/>
-      <x:c r="G9" s="6"/>
-      <x:c r="H9" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="3"/>
-      <x:c r="J9" s="3"/>
-      <x:c r="K9" s="3"/>
-      <x:c r="L9" s="3"/>
-      <x:c r="M9" s="3"/>
-      <x:c r="N9" s="3"/>
-      <x:c r="O9" s="3"/>
-      <x:c r="P9" s="3"/>
-      <x:c r="Q9" s="3"/>
-      <x:c r="R9" s="3"/>
-    </x:row>
-    <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A10" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B10" s="7"/>
-      <x:c r="C10" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="7"/>
-      <x:c r="E10" s="7"/>
-      <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7"/>
-      <x:c r="H10" s="7"/>
-      <x:c r="I10" s="3"/>
-      <x:c r="J10" s="3"/>
-      <x:c r="K10" s="3"/>
-      <x:c r="L10" s="3"/>
-      <x:c r="M10" s="3"/>
-      <x:c r="N10" s="3"/>
-      <x:c r="O10" s="3"/>
-      <x:c r="P10" s="3"/>
-      <x:c r="Q10" s="3"/>
-      <x:c r="R10" s="3"/>
+      <x:c r="D10" s="8"/>
+      <x:c r="E10" s="8"/>
+      <x:c r="F10" s="8"/>
+      <x:c r="G10" s="8"/>
+      <x:c r="H10" s="8"/>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="4"/>
+      <x:c r="K10" s="4"/>
+      <x:c r="L10" s="4"/>
+      <x:c r="M10" s="4"/>
+      <x:c r="N10" s="4"/>
+      <x:c r="O10" s="4"/>
+      <x:c r="P10" s="4"/>
+      <x:c r="Q10" s="4"/>
+      <x:c r="R10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
-      <x:c r="D11" s="7"/>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7"/>
-      <x:c r="I11" s="3"/>
-      <x:c r="J11" s="3"/>
-      <x:c r="K11" s="3"/>
-      <x:c r="L11" s="3"/>
-      <x:c r="M11" s="3"/>
-      <x:c r="N11" s="3"/>
-      <x:c r="O11" s="3"/>
-      <x:c r="P11" s="3"/>
-      <x:c r="Q11" s="3"/>
-      <x:c r="R11" s="3"/>
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="8"/>
+      <x:c r="C11" s="8"/>
+      <x:c r="D11" s="8"/>
+      <x:c r="E11" s="8"/>
+      <x:c r="F11" s="8"/>
+      <x:c r="G11" s="8"/>
+      <x:c r="H11" s="8"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+      <x:c r="L11" s="4"/>
+      <x:c r="M11" s="4"/>
+      <x:c r="N11" s="4"/>
+      <x:c r="O11" s="4"/>
+      <x:c r="P11" s="4"/>
+      <x:c r="Q11" s="4"/>
+      <x:c r="R11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
-      <x:c r="D12" s="6"/>
-      <x:c r="E12" s="6"/>
-      <x:c r="F12" s="6"/>
-      <x:c r="G12" s="6"/>
-      <x:c r="H12" s="6"/>
-      <x:c r="I12" s="3"/>
-      <x:c r="J12" s="3"/>
-      <x:c r="K12" s="3"/>
-      <x:c r="L12" s="3"/>
-      <x:c r="M12" s="3"/>
-      <x:c r="N12" s="3"/>
-      <x:c r="O12" s="3"/>
-      <x:c r="P12" s="3"/>
-      <x:c r="Q12" s="3"/>
-      <x:c r="R12" s="3"/>
+      <x:c r="A12" s="7"/>
+      <x:c r="B12" s="7"/>
+      <x:c r="C12" s="7"/>
+      <x:c r="D12" s="7"/>
+      <x:c r="E12" s="7"/>
+      <x:c r="F12" s="7"/>
+      <x:c r="G12" s="7"/>
+      <x:c r="H12" s="7"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+      <x:c r="L12" s="4"/>
+      <x:c r="M12" s="4"/>
+      <x:c r="N12" s="4"/>
+      <x:c r="O12" s="4"/>
+      <x:c r="P12" s="4"/>
+      <x:c r="Q12" s="4"/>
+      <x:c r="R12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="3"/>
-      <x:c r="J13" s="3"/>
-      <x:c r="K13" s="3"/>
-      <x:c r="L13" s="3"/>
-      <x:c r="M13" s="3"/>
-      <x:c r="N13" s="3"/>
-      <x:c r="O13" s="3"/>
-      <x:c r="P13" s="3"/>
-      <x:c r="Q13" s="3"/>
-      <x:c r="R13" s="3"/>
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5"/>
+      <x:c r="C13" s="5"/>
+      <x:c r="D13" s="5"/>
+      <x:c r="E13" s="5"/>
+      <x:c r="F13" s="5"/>
+      <x:c r="G13" s="5"/>
+      <x:c r="H13" s="5"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+      <x:c r="L13" s="4"/>
+      <x:c r="M13" s="4"/>
+      <x:c r="N13" s="4"/>
+      <x:c r="O13" s="4"/>
+      <x:c r="P13" s="4"/>
+      <x:c r="Q13" s="4"/>
+      <x:c r="R13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="7"/>
-      <x:c r="C14" s="7"/>
-      <x:c r="D14" s="7"/>
-      <x:c r="E14" s="7"/>
-      <x:c r="F14" s="7"/>
-      <x:c r="G14" s="7"/>
-      <x:c r="H14" s="7"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-      <x:c r="L14" s="3"/>
-      <x:c r="M14" s="3"/>
-      <x:c r="N14" s="3"/>
-      <x:c r="O14" s="3"/>
-      <x:c r="P14" s="3"/>
-      <x:c r="Q14" s="3"/>
-      <x:c r="R14" s="3"/>
+      <x:c r="A14" s="8"/>
+      <x:c r="B14" s="8"/>
+      <x:c r="C14" s="8"/>
+      <x:c r="D14" s="8"/>
+      <x:c r="E14" s="8"/>
+      <x:c r="F14" s="8"/>
+      <x:c r="G14" s="8"/>
+      <x:c r="H14" s="8"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+      <x:c r="L14" s="4"/>
+      <x:c r="M14" s="4"/>
+      <x:c r="N14" s="4"/>
+      <x:c r="O14" s="4"/>
+      <x:c r="P14" s="4"/>
+      <x:c r="Q14" s="4"/>
+      <x:c r="R14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A15" s="7"/>
-      <x:c r="B15" s="7"/>
-      <x:c r="C15" s="7"/>
-      <x:c r="D15" s="7"/>
-      <x:c r="E15" s="7"/>
-      <x:c r="F15" s="7"/>
-      <x:c r="G15" s="7"/>
-      <x:c r="H15" s="7"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
-      <x:c r="L15" s="3"/>
-      <x:c r="M15" s="3"/>
-      <x:c r="N15" s="3"/>
-      <x:c r="O15" s="3"/>
-      <x:c r="P15" s="3"/>
-      <x:c r="Q15" s="3"/>
-      <x:c r="R15" s="3"/>
+      <x:c r="A15" s="8"/>
+      <x:c r="B15" s="8"/>
+      <x:c r="C15" s="8"/>
+      <x:c r="D15" s="8"/>
+      <x:c r="E15" s="8"/>
+      <x:c r="F15" s="8"/>
+      <x:c r="G15" s="8"/>
+      <x:c r="H15" s="8"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+      <x:c r="L15" s="4"/>
+      <x:c r="M15" s="4"/>
+      <x:c r="N15" s="4"/>
+      <x:c r="O15" s="4"/>
+      <x:c r="P15" s="4"/>
+      <x:c r="Q15" s="4"/>
+      <x:c r="R15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A16" s="8"/>
-      <x:c r="B16" s="8"/>
-      <x:c r="C16" s="8"/>
-      <x:c r="D16" s="8"/>
-      <x:c r="E16" s="8"/>
-      <x:c r="F16" s="8"/>
-      <x:c r="G16" s="8"/>
-      <x:c r="H16" s="8"/>
+      <x:c r="A16" s="9"/>
+      <x:c r="B16" s="9"/>
+      <x:c r="C16" s="9"/>
+      <x:c r="D16" s="9"/>
+      <x:c r="E16" s="9"/>
+      <x:c r="F16" s="9"/>
+      <x:c r="G16" s="9"/>
+      <x:c r="H16" s="9"/>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A17" s="9"/>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-      <x:c r="D17" s="8"/>
-      <x:c r="E17" s="8"/>
-      <x:c r="F17" s="8"/>
-      <x:c r="G17" s="9"/>
-      <x:c r="H17" s="9"/>
+      <x:c r="A17" s="10"/>
+      <x:c r="B17" s="10"/>
+      <x:c r="C17" s="10"/>
+      <x:c r="D17" s="9"/>
+      <x:c r="E17" s="9"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="G17" s="10"/>
+      <x:c r="H17" s="10"/>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A18" s="9"/>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="8"/>
-      <x:c r="E18" s="8"/>
-      <x:c r="F18" s="8"/>
-      <x:c r="G18" s="9"/>
-      <x:c r="H18" s="9"/>
+      <x:c r="A18" s="10"/>
+      <x:c r="B18" s="10"/>
+      <x:c r="C18" s="10"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="10"/>
+      <x:c r="H18" s="10"/>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A19" s="9"/>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="8"/>
-      <x:c r="E19" s="8"/>
-      <x:c r="F19" s="8"/>
-      <x:c r="G19" s="9"/>
-      <x:c r="H19" s="9"/>
+      <x:c r="A19" s="10"/>
+      <x:c r="B19" s="10"/>
+      <x:c r="C19" s="10"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="10"/>
+      <x:c r="H19" s="10"/>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A20" s="9"/>
-      <x:c r="B20" s="9"/>
-      <x:c r="C20" s="9"/>
-      <x:c r="D20" s="8"/>
-      <x:c r="E20" s="8"/>
-      <x:c r="F20" s="8"/>
-      <x:c r="G20" s="9"/>
-      <x:c r="H20" s="9"/>
+      <x:c r="A20" s="10"/>
+      <x:c r="B20" s="10"/>
+      <x:c r="C20" s="10"/>
+      <x:c r="D20" s="9"/>
+      <x:c r="E20" s="9"/>
+      <x:c r="F20" s="9"/>
+      <x:c r="G20" s="10"/>
+      <x:c r="H20" s="10"/>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A21" s="9"/>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
-      <x:c r="D21" s="8"/>
-      <x:c r="E21" s="8"/>
-      <x:c r="F21" s="8"/>
-      <x:c r="G21" s="9"/>
-      <x:c r="H21" s="9"/>
+      <x:c r="A21" s="10"/>
+      <x:c r="B21" s="10"/>
+      <x:c r="C21" s="10"/>
+      <x:c r="D21" s="9"/>
+      <x:c r="E21" s="9"/>
+      <x:c r="F21" s="9"/>
+      <x:c r="G21" s="10"/>
+      <x:c r="H21" s="10"/>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A22" s="9"/>
-      <x:c r="B22" s="9"/>
-      <x:c r="C22" s="9"/>
-      <x:c r="D22" s="8"/>
-      <x:c r="E22" s="8"/>
-      <x:c r="F22" s="8"/>
-      <x:c r="G22" s="9"/>
-      <x:c r="H22" s="9"/>
+      <x:c r="A22" s="10"/>
+      <x:c r="B22" s="10"/>
+      <x:c r="C22" s="10"/>
+      <x:c r="D22" s="9"/>
+      <x:c r="E22" s="9"/>
+      <x:c r="F22" s="9"/>
+      <x:c r="G22" s="10"/>
+      <x:c r="H22" s="10"/>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A23" s="9"/>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
-      <x:c r="D23" s="8"/>
-      <x:c r="E23" s="8"/>
-      <x:c r="F23" s="8"/>
-      <x:c r="G23" s="9"/>
-      <x:c r="H23" s="9"/>
+      <x:c r="A23" s="10"/>
+      <x:c r="B23" s="10"/>
+      <x:c r="C23" s="10"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="G23" s="10"/>
+      <x:c r="H23" s="10"/>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A24" s="9"/>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-      <x:c r="D24" s="8"/>
-      <x:c r="E24" s="8"/>
-      <x:c r="F24" s="8"/>
-      <x:c r="G24" s="9"/>
-      <x:c r="H24" s="9"/>
+      <x:c r="A24" s="10"/>
+      <x:c r="B24" s="10"/>
+      <x:c r="C24" s="10"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="G24" s="10"/>
+      <x:c r="H24" s="10"/>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A25" s="9"/>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
-      <x:c r="D25" s="8"/>
-      <x:c r="E25" s="8"/>
-      <x:c r="F25" s="8"/>
-      <x:c r="G25" s="9"/>
-      <x:c r="H25" s="9"/>
+      <x:c r="A25" s="10"/>
+      <x:c r="B25" s="10"/>
+      <x:c r="C25" s="10"/>
+      <x:c r="D25" s="9"/>
+      <x:c r="E25" s="9"/>
+      <x:c r="F25" s="9"/>
+      <x:c r="G25" s="10"/>
+      <x:c r="H25" s="10"/>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A26" s="10"/>
-      <x:c r="B26" s="10"/>
-      <x:c r="C26" s="10"/>
-      <x:c r="D26" s="10"/>
-      <x:c r="E26" s="10"/>
-      <x:c r="F26" s="10"/>
-      <x:c r="G26" s="10"/>
-      <x:c r="H26" s="10"/>
+      <x:c r="A26" s="11"/>
+      <x:c r="B26" s="11"/>
+      <x:c r="C26" s="11"/>
+      <x:c r="D26" s="11"/>
+      <x:c r="E26" s="11"/>
+      <x:c r="F26" s="11"/>
+      <x:c r="G26" s="11"/>
+      <x:c r="H26" s="11"/>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A27" s="10"/>
-      <x:c r="B27" s="10"/>
-      <x:c r="C27" s="10"/>
-      <x:c r="D27" s="10"/>
-      <x:c r="E27" s="10"/>
-      <x:c r="F27" s="10"/>
-      <x:c r="G27" s="10"/>
-      <x:c r="H27" s="10"/>
+      <x:c r="A27" s="11"/>
+      <x:c r="B27" s="11"/>
+      <x:c r="C27" s="11"/>
+      <x:c r="D27" s="11"/>
+      <x:c r="E27" s="11"/>
+      <x:c r="F27" s="11"/>
+      <x:c r="G27" s="11"/>
+      <x:c r="H27" s="11"/>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A28" s="10"/>
-      <x:c r="B28" s="10"/>
-      <x:c r="C28" s="10"/>
-      <x:c r="D28" s="10"/>
-      <x:c r="E28" s="10"/>
-      <x:c r="F28" s="10"/>
-      <x:c r="G28" s="10"/>
-      <x:c r="H28" s="10"/>
+      <x:c r="A28" s="11"/>
+      <x:c r="B28" s="11"/>
+      <x:c r="C28" s="11"/>
+      <x:c r="D28" s="11"/>
+      <x:c r="E28" s="11"/>
+      <x:c r="F28" s="11"/>
+      <x:c r="G28" s="11"/>
+      <x:c r="H28" s="11"/>
     </x:row>
     <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A29" s="10"/>
-      <x:c r="B29" s="10"/>
-      <x:c r="C29" s="10"/>
-      <x:c r="D29" s="10"/>
-      <x:c r="E29" s="10"/>
-      <x:c r="F29" s="10"/>
-      <x:c r="G29" s="10"/>
-      <x:c r="H29" s="10"/>
+      <x:c r="A29" s="11"/>
+      <x:c r="B29" s="11"/>
+      <x:c r="C29" s="11"/>
+      <x:c r="D29" s="11"/>
+      <x:c r="E29" s="11"/>
+      <x:c r="F29" s="11"/>
+      <x:c r="G29" s="11"/>
+      <x:c r="H29" s="11"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A30" s="10"/>
-      <x:c r="B30" s="10"/>
-      <x:c r="C30" s="10"/>
-      <x:c r="D30" s="10"/>
-      <x:c r="E30" s="10"/>
-      <x:c r="F30" s="10"/>
-      <x:c r="G30" s="10"/>
-      <x:c r="H30" s="10"/>
+      <x:c r="A30" s="11"/>
+      <x:c r="B30" s="11"/>
+      <x:c r="C30" s="11"/>
+      <x:c r="D30" s="11"/>
+      <x:c r="E30" s="11"/>
+      <x:c r="F30" s="11"/>
+      <x:c r="G30" s="11"/>
+      <x:c r="H30" s="11"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A31" s="10"/>
-      <x:c r="B31" s="10"/>
-      <x:c r="C31" s="10"/>
-      <x:c r="D31" s="10"/>
-      <x:c r="E31" s="10"/>
-      <x:c r="F31" s="10"/>
-      <x:c r="G31" s="10"/>
-      <x:c r="H31" s="10"/>
+      <x:c r="A31" s="11"/>
+      <x:c r="B31" s="11"/>
+      <x:c r="C31" s="11"/>
+      <x:c r="D31" s="11"/>
+      <x:c r="E31" s="11"/>
+      <x:c r="F31" s="11"/>
+      <x:c r="G31" s="11"/>
+      <x:c r="H31" s="11"/>
     </x:row>
     <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
-      <x:c r="D32" s="11"/>
-      <x:c r="E32" s="11"/>
-      <x:c r="F32" s="11"/>
-      <x:c r="G32" s="11"/>
-      <x:c r="H32" s="11"/>
+      <x:c r="A32" s="12"/>
+      <x:c r="B32" s="12"/>
+      <x:c r="C32" s="12"/>
+      <x:c r="D32" s="12"/>
+      <x:c r="E32" s="12"/>
+      <x:c r="F32" s="12"/>
+      <x:c r="G32" s="12"/>
+      <x:c r="H32" s="12"/>
     </x:row>
     <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
-      <x:c r="D33" s="11"/>
-      <x:c r="E33" s="11"/>
-      <x:c r="F33" s="11"/>
-      <x:c r="G33" s="11"/>
-      <x:c r="H33" s="11"/>
+      <x:c r="A33" s="12"/>
+      <x:c r="B33" s="12"/>
+      <x:c r="C33" s="12"/>
+      <x:c r="D33" s="12"/>
+      <x:c r="E33" s="12"/>
+      <x:c r="F33" s="12"/>
+      <x:c r="G33" s="12"/>
+      <x:c r="H33" s="12"/>
     </x:row>
     <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
-      <x:c r="D34" s="11"/>
-      <x:c r="E34" s="11"/>
-      <x:c r="F34" s="11"/>
-      <x:c r="G34" s="11"/>
-      <x:c r="H34" s="11"/>
+      <x:c r="A34" s="12"/>
+      <x:c r="B34" s="12"/>
+      <x:c r="C34" s="12"/>
+      <x:c r="D34" s="12"/>
+      <x:c r="E34" s="12"/>
+      <x:c r="F34" s="12"/>
+      <x:c r="G34" s="12"/>
+      <x:c r="H34" s="12"/>
     </x:row>
     <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
-      <x:c r="D35" s="11"/>
-      <x:c r="E35" s="11"/>
-      <x:c r="F35" s="11"/>
-      <x:c r="G35" s="11"/>
-      <x:c r="H35" s="11"/>
+      <x:c r="A35" s="12"/>
+      <x:c r="B35" s="12"/>
+      <x:c r="C35" s="12"/>
+      <x:c r="D35" s="12"/>
+      <x:c r="E35" s="12"/>
+      <x:c r="F35" s="12"/>
+      <x:c r="G35" s="12"/>
+      <x:c r="H35" s="12"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
@@ -1994,7 +2393,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21825" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -19,103 +19,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+  <x:si>
+    <x:t>한달 묵은것치곤 많이 허술한 뱀이였다..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여긴 어디지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 대답하지 않는다,대답한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_ellie_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_enterbattle_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭔가 한달 내내 본것같은 지긋지긋한 느낌이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거대한 뱀이 공격해온다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제의 세계에 접속했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
   <x:si>
     <x:t>NextDialogueId</x:t>
   </x:si>
   <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제의 세계에 접속했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 대답하지 않는다,대답한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+    <x:t>분명 처음 보는 풍경인데</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 쓰러트렸으니 돌아갈 수 있을것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
   </x:si>
   <x:si>
     <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -147,12 +186,7 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:name val="Arial"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
     </x:font>
@@ -166,8 +200,14 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffc6efce"/>
-        <x:bgColor rgb="ffc6efce"/>
+        <x:fgColor rgb="ffffffff"/>
+        <x:bgColor rgb="ffffc000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffffff"/>
+        <x:bgColor rgb="ffd86dcd"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -178,14 +218,8 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffffc000"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffd86dcd"/>
+        <x:fgColor rgb="ffc6efce"/>
+        <x:bgColor rgb="ffc6efce"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -237,38 +271,38 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -874,7 +908,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:R35"/>
+  <x:dimension ref="A1:V35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" style="1" customWidth="1"/>
@@ -883,549 +917,957 @@
     <x:col min="7" max="8" width="50.7265625" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A1" s="2" t="s">
+    <x:row r="1" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A1" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B1" s="6"/>
+      <x:c r="C1" s="6"/>
+      <x:c r="D1" s="6"/>
+      <x:c r="E1" s="6"/>
+      <x:c r="F1" s="6"/>
+      <x:c r="G1" s="6"/>
+      <x:c r="H1" s="6"/>
+      <x:c r="I1" s="7"/>
+      <x:c r="J1" s="7"/>
+      <x:c r="K1" s="7"/>
+      <x:c r="L1" s="7"/>
+      <x:c r="M1" s="7"/>
+      <x:c r="N1" s="7"/>
+      <x:c r="O1" s="7"/>
+      <x:c r="P1" s="7"/>
+      <x:c r="Q1" s="7"/>
+      <x:c r="R1" s="7"/>
+      <x:c r="S1" s="7"/>
+      <x:c r="T1" s="7"/>
+      <x:c r="U1" s="7"/>
+      <x:c r="V1" s="7"/>
+    </x:row>
+    <x:row r="2" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A2" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I2" s="7"/>
+      <x:c r="J2" s="7"/>
+      <x:c r="K2" s="7"/>
+      <x:c r="L2" s="7"/>
+      <x:c r="M2" s="7"/>
+      <x:c r="N2" s="7"/>
+      <x:c r="O2" s="7"/>
+      <x:c r="P2" s="7"/>
+      <x:c r="Q2" s="7"/>
+      <x:c r="R2" s="7"/>
+      <x:c r="S2" s="7"/>
+      <x:c r="T2" s="7"/>
+      <x:c r="U2" s="7"/>
+      <x:c r="V2" s="7"/>
+    </x:row>
+    <x:row r="3" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A3" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I3" s="7"/>
+      <x:c r="J3" s="7"/>
+      <x:c r="K3" s="7"/>
+      <x:c r="L3" s="7"/>
+      <x:c r="M3" s="7"/>
+      <x:c r="N3" s="7"/>
+      <x:c r="O3" s="7"/>
+      <x:c r="P3" s="7"/>
+      <x:c r="Q3" s="7"/>
+      <x:c r="R3" s="7"/>
+      <x:c r="S3" s="7"/>
+      <x:c r="T3" s="7"/>
+      <x:c r="U3" s="7"/>
+      <x:c r="V3" s="7"/>
+    </x:row>
+    <x:row r="4" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A4" s="9" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B4" s="10"/>
+      <x:c r="C4" s="9" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H4" s="9"/>
+      <x:c r="I4" s="2"/>
+      <x:c r="J4" s="2"/>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2"/>
+      <x:c r="N4" s="2"/>
+      <x:c r="O4" s="2"/>
+      <x:c r="P4" s="2"/>
+      <x:c r="Q4" s="2"/>
+      <x:c r="R4" s="2"/>
+      <x:c r="S4" s="7"/>
+      <x:c r="T4" s="7"/>
+      <x:c r="U4" s="7"/>
+      <x:c r="V4" s="7"/>
+    </x:row>
+    <x:row r="5" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A5" s="9" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B5" s="10"/>
+      <x:c r="C5" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E5" s="9"/>
+      <x:c r="F5" s="9"/>
+      <x:c r="G5" s="9"/>
+      <x:c r="H5" s="9"/>
+      <x:c r="I5" s="2"/>
+      <x:c r="J5" s="2"/>
+      <x:c r="K5" s="2"/>
+      <x:c r="L5" s="2"/>
+      <x:c r="M5" s="2"/>
+      <x:c r="N5" s="2"/>
+      <x:c r="O5" s="2"/>
+      <x:c r="P5" s="2"/>
+      <x:c r="Q5" s="2"/>
+      <x:c r="R5" s="2"/>
+      <x:c r="S5" s="7"/>
+      <x:c r="T5" s="7"/>
+      <x:c r="U5" s="7"/>
+      <x:c r="V5" s="7"/>
+    </x:row>
+    <x:row r="6" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A6" s="9" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B6" s="10"/>
+      <x:c r="C6" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D6" s="9"/>
+      <x:c r="E6" s="9"/>
+      <x:c r="F6" s="9"/>
+      <x:c r="G6" s="9"/>
+      <x:c r="H6" s="9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I6" s="2"/>
+      <x:c r="J6" s="2"/>
+      <x:c r="K6" s="2"/>
+      <x:c r="L6" s="2"/>
+      <x:c r="M6" s="2"/>
+      <x:c r="N6" s="2"/>
+      <x:c r="O6" s="2"/>
+      <x:c r="P6" s="2"/>
+      <x:c r="Q6" s="2"/>
+      <x:c r="R6" s="2"/>
+      <x:c r="S6" s="7"/>
+      <x:c r="T6" s="7"/>
+      <x:c r="U6" s="7"/>
+      <x:c r="V6" s="7"/>
+    </x:row>
+    <x:row r="7" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A7" s="9" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="9"/>
+      <x:c r="C7" s="9" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-      <x:c r="D1" s="2"/>
-      <x:c r="E1" s="2"/>
-      <x:c r="F1" s="2"/>
-      <x:c r="G1" s="2"/>
-      <x:c r="H1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="D7" s="9"/>
+      <x:c r="E7" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="2"/>
+      <x:c r="J7" s="2"/>
+      <x:c r="K7" s="2"/>
+      <x:c r="L7" s="2"/>
+      <x:c r="M7" s="2"/>
+      <x:c r="N7" s="2"/>
+      <x:c r="O7" s="2"/>
+      <x:c r="P7" s="2"/>
+      <x:c r="Q7" s="2"/>
+      <x:c r="R7" s="2"/>
+      <x:c r="S7" s="7"/>
+      <x:c r="T7" s="7"/>
+      <x:c r="U7" s="7"/>
+      <x:c r="V7" s="7"/>
+    </x:row>
+    <x:row r="8" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A8" s="9" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="11"/>
+      <x:c r="C8" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="11"/>
+      <x:c r="E8" s="11"/>
+      <x:c r="F8" s="11"/>
+      <x:c r="G8" s="11"/>
+      <x:c r="H8" s="11"/>
+      <x:c r="I8" s="2"/>
+      <x:c r="J8" s="2"/>
+      <x:c r="K8" s="2"/>
+      <x:c r="L8" s="2"/>
+      <x:c r="M8" s="2"/>
+      <x:c r="N8" s="2"/>
+      <x:c r="O8" s="2"/>
+      <x:c r="P8" s="2"/>
+      <x:c r="Q8" s="2"/>
+      <x:c r="R8" s="2"/>
+      <x:c r="S8" s="7"/>
+      <x:c r="T8" s="7"/>
+      <x:c r="U8" s="7"/>
+      <x:c r="V8" s="7"/>
+    </x:row>
+    <x:row r="9" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A9" s="9" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="11"/>
+      <x:c r="C9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
+      <x:c r="D9" s="11"/>
+      <x:c r="E9" s="11"/>
+      <x:c r="F9" s="11"/>
+      <x:c r="G9" s="11"/>
+      <x:c r="H9" s="9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I9" s="2"/>
+      <x:c r="J9" s="2"/>
+      <x:c r="K9" s="2"/>
+      <x:c r="L9" s="2"/>
+      <x:c r="M9" s="2"/>
+      <x:c r="N9" s="2"/>
+      <x:c r="O9" s="2"/>
+      <x:c r="P9" s="2"/>
+      <x:c r="Q9" s="2"/>
+      <x:c r="R9" s="2"/>
+      <x:c r="S9" s="7"/>
+      <x:c r="T9" s="7"/>
+      <x:c r="U9" s="7"/>
+      <x:c r="V9" s="7"/>
+    </x:row>
+    <x:row r="10" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A10" s="9" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B10" s="12"/>
+      <x:c r="C10" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="12"/>
+      <x:c r="E10" s="12"/>
+      <x:c r="F10" s="12"/>
+      <x:c r="G10" s="12"/>
+      <x:c r="H10" s="12"/>
+      <x:c r="I10" s="2"/>
+      <x:c r="J10" s="2"/>
+      <x:c r="K10" s="2"/>
+      <x:c r="L10" s="2"/>
+      <x:c r="M10" s="2"/>
+      <x:c r="N10" s="2"/>
+      <x:c r="O10" s="2"/>
+      <x:c r="P10" s="2"/>
+      <x:c r="Q10" s="2"/>
+      <x:c r="R10" s="2"/>
+      <x:c r="S10" s="7"/>
+      <x:c r="T10" s="7"/>
+      <x:c r="U10" s="7"/>
+      <x:c r="V10" s="7"/>
+    </x:row>
+    <x:row r="11" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A11" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E11" s="12"/>
+      <x:c r="F11" s="12"/>
+      <x:c r="G11" s="12"/>
+      <x:c r="H11" s="12"/>
+      <x:c r="I11" s="2"/>
+      <x:c r="J11" s="2"/>
+      <x:c r="K11" s="2"/>
+      <x:c r="L11" s="2"/>
+      <x:c r="M11" s="2"/>
+      <x:c r="N11" s="2"/>
+      <x:c r="O11" s="2"/>
+      <x:c r="P11" s="2"/>
+      <x:c r="Q11" s="2"/>
+      <x:c r="R11" s="2"/>
+      <x:c r="S11" s="7"/>
+      <x:c r="T11" s="7"/>
+      <x:c r="U11" s="7"/>
+      <x:c r="V11" s="7"/>
+    </x:row>
+    <x:row r="12" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A12" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E12" s="11"/>
+      <x:c r="F12" s="11"/>
+      <x:c r="G12" s="11"/>
+      <x:c r="H12" s="11"/>
+      <x:c r="I12" s="2"/>
+      <x:c r="J12" s="2"/>
+      <x:c r="K12" s="2"/>
+      <x:c r="L12" s="2"/>
+      <x:c r="M12" s="2"/>
+      <x:c r="N12" s="2"/>
+      <x:c r="O12" s="2"/>
+      <x:c r="P12" s="2"/>
+      <x:c r="Q12" s="2"/>
+      <x:c r="R12" s="2"/>
+      <x:c r="S12" s="7"/>
+      <x:c r="T12" s="7"/>
+      <x:c r="U12" s="7"/>
+      <x:c r="V12" s="7"/>
+    </x:row>
+    <x:row r="13" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A13" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="9"/>
+      <x:c r="H13" s="9"/>
+      <x:c r="I13" s="2"/>
+      <x:c r="J13" s="2"/>
+      <x:c r="K13" s="2"/>
+      <x:c r="L13" s="2"/>
+      <x:c r="M13" s="2"/>
+      <x:c r="N13" s="2"/>
+      <x:c r="O13" s="2"/>
+      <x:c r="P13" s="2"/>
+      <x:c r="Q13" s="2"/>
+      <x:c r="R13" s="2"/>
+      <x:c r="S13" s="7"/>
+      <x:c r="T13" s="7"/>
+      <x:c r="U13" s="7"/>
+      <x:c r="V13" s="7"/>
+    </x:row>
+    <x:row r="14" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A14" s="12" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B14" s="12"/>
+      <x:c r="C14" s="12" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D14" s="12"/>
+      <x:c r="E14" s="12"/>
+      <x:c r="F14" s="12"/>
+      <x:c r="G14" s="12"/>
+      <x:c r="H14" s="12"/>
+      <x:c r="I14" s="2"/>
+      <x:c r="J14" s="2"/>
+      <x:c r="K14" s="2"/>
+      <x:c r="L14" s="2"/>
+      <x:c r="M14" s="2"/>
+      <x:c r="N14" s="2"/>
+      <x:c r="O14" s="2"/>
+      <x:c r="P14" s="2"/>
+      <x:c r="Q14" s="2"/>
+      <x:c r="R14" s="2"/>
+      <x:c r="S14" s="7"/>
+      <x:c r="T14" s="7"/>
+      <x:c r="U14" s="7"/>
+      <x:c r="V14" s="7"/>
+    </x:row>
+    <x:row r="15" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A15" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
+      <x:c r="B15" s="12"/>
+      <x:c r="C15" s="12" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A4" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="6"/>
-      <x:c r="C4" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
-      <x:c r="L4" s="4"/>
-      <x:c r="M4" s="4"/>
-      <x:c r="N4" s="4"/>
-      <x:c r="O4" s="4"/>
-      <x:c r="P4" s="4"/>
-      <x:c r="Q4" s="4"/>
-      <x:c r="R4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A5" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="6"/>
-      <x:c r="C5" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="4"/>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
-      <x:c r="L5" s="4"/>
-      <x:c r="M5" s="4"/>
-      <x:c r="N5" s="4"/>
-      <x:c r="O5" s="4"/>
-      <x:c r="P5" s="4"/>
-      <x:c r="Q5" s="4"/>
-      <x:c r="R5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A6" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B6" s="6"/>
-      <x:c r="C6" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
-      <x:c r="G6" s="5"/>
-      <x:c r="H6" s="5" t="s">
+      <x:c r="D15" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I6" s="4"/>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4"/>
-      <x:c r="L6" s="4"/>
-      <x:c r="M6" s="4"/>
-      <x:c r="N6" s="4"/>
-      <x:c r="O6" s="4"/>
-      <x:c r="P6" s="4"/>
-      <x:c r="Q6" s="4"/>
-      <x:c r="R6" s="4"/>
-    </x:row>
-    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B7" s="5"/>
-      <x:c r="C7" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="5"/>
-      <x:c r="E7" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F7" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
-      <x:c r="L7" s="4"/>
-      <x:c r="M7" s="4"/>
-      <x:c r="N7" s="4"/>
-      <x:c r="O7" s="4"/>
-      <x:c r="P7" s="4"/>
-      <x:c r="Q7" s="4"/>
-      <x:c r="R7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="7"/>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7"/>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
-      <x:c r="L8" s="4"/>
-      <x:c r="M8" s="4"/>
-      <x:c r="N8" s="4"/>
-      <x:c r="O8" s="4"/>
-      <x:c r="P8" s="4"/>
-      <x:c r="Q8" s="4"/>
-      <x:c r="R8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B9" s="7"/>
-      <x:c r="C9" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D9" s="7"/>
-      <x:c r="E9" s="7"/>
-      <x:c r="F9" s="7"/>
-      <x:c r="G9" s="7"/>
-      <x:c r="H9" s="5" t="s">
+      <x:c r="E15" s="12"/>
+      <x:c r="F15" s="12"/>
+      <x:c r="G15" s="12"/>
+      <x:c r="H15" s="12"/>
+      <x:c r="I15" s="2"/>
+      <x:c r="J15" s="2"/>
+      <x:c r="K15" s="2"/>
+      <x:c r="L15" s="2"/>
+      <x:c r="M15" s="2"/>
+      <x:c r="N15" s="2"/>
+      <x:c r="O15" s="2"/>
+      <x:c r="P15" s="2"/>
+      <x:c r="Q15" s="2"/>
+      <x:c r="R15" s="2"/>
+      <x:c r="S15" s="7"/>
+      <x:c r="T15" s="7"/>
+      <x:c r="U15" s="7"/>
+      <x:c r="V15" s="7"/>
+    </x:row>
+    <x:row r="16" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A16" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
-      <x:c r="L9" s="4"/>
-      <x:c r="M9" s="4"/>
-      <x:c r="N9" s="4"/>
-      <x:c r="O9" s="4"/>
-      <x:c r="P9" s="4"/>
-      <x:c r="Q9" s="4"/>
-      <x:c r="R9" s="4"/>
-    </x:row>
-    <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A10" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B10" s="8"/>
-      <x:c r="C10" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D10" s="8"/>
-      <x:c r="E10" s="8"/>
-      <x:c r="F10" s="8"/>
-      <x:c r="G10" s="8"/>
-      <x:c r="H10" s="8"/>
-      <x:c r="I10" s="4"/>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
-      <x:c r="L10" s="4"/>
-      <x:c r="M10" s="4"/>
-      <x:c r="N10" s="4"/>
-      <x:c r="O10" s="4"/>
-      <x:c r="P10" s="4"/>
-      <x:c r="Q10" s="4"/>
-      <x:c r="R10" s="4"/>
-    </x:row>
-    <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A11" s="8"/>
-      <x:c r="B11" s="8"/>
-      <x:c r="C11" s="8"/>
-      <x:c r="D11" s="8"/>
-      <x:c r="E11" s="8"/>
-      <x:c r="F11" s="8"/>
-      <x:c r="G11" s="8"/>
-      <x:c r="H11" s="8"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-      <x:c r="L11" s="4"/>
-      <x:c r="M11" s="4"/>
-      <x:c r="N11" s="4"/>
-      <x:c r="O11" s="4"/>
-      <x:c r="P11" s="4"/>
-      <x:c r="Q11" s="4"/>
-      <x:c r="R11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
-      <x:c r="D12" s="7"/>
-      <x:c r="E12" s="7"/>
-      <x:c r="F12" s="7"/>
-      <x:c r="G12" s="7"/>
-      <x:c r="H12" s="7"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-      <x:c r="L12" s="4"/>
-      <x:c r="M12" s="4"/>
-      <x:c r="N12" s="4"/>
-      <x:c r="O12" s="4"/>
-      <x:c r="P12" s="4"/>
-      <x:c r="Q12" s="4"/>
-      <x:c r="R12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A13" s="5"/>
-      <x:c r="B13" s="5"/>
-      <x:c r="C13" s="5"/>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-      <x:c r="L13" s="4"/>
-      <x:c r="M13" s="4"/>
-      <x:c r="N13" s="4"/>
-      <x:c r="O13" s="4"/>
-      <x:c r="P13" s="4"/>
-      <x:c r="Q13" s="4"/>
-      <x:c r="R13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A14" s="8"/>
-      <x:c r="B14" s="8"/>
-      <x:c r="C14" s="8"/>
-      <x:c r="D14" s="8"/>
-      <x:c r="E14" s="8"/>
-      <x:c r="F14" s="8"/>
-      <x:c r="G14" s="8"/>
-      <x:c r="H14" s="8"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-      <x:c r="L14" s="4"/>
-      <x:c r="M14" s="4"/>
-      <x:c r="N14" s="4"/>
-      <x:c r="O14" s="4"/>
-      <x:c r="P14" s="4"/>
-      <x:c r="Q14" s="4"/>
-      <x:c r="R14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A15" s="8"/>
-      <x:c r="B15" s="8"/>
-      <x:c r="C15" s="8"/>
-      <x:c r="D15" s="8"/>
-      <x:c r="E15" s="8"/>
-      <x:c r="F15" s="8"/>
-      <x:c r="G15" s="8"/>
-      <x:c r="H15" s="8"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-      <x:c r="L15" s="4"/>
-      <x:c r="M15" s="4"/>
-      <x:c r="N15" s="4"/>
-      <x:c r="O15" s="4"/>
-      <x:c r="P15" s="4"/>
-      <x:c r="Q15" s="4"/>
-      <x:c r="R15" s="4"/>
-    </x:row>
-    <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A16" s="9"/>
-      <x:c r="B16" s="9"/>
-      <x:c r="C16" s="9"/>
-      <x:c r="D16" s="9"/>
-      <x:c r="E16" s="9"/>
-      <x:c r="F16" s="9"/>
-      <x:c r="G16" s="9"/>
-      <x:c r="H16" s="9"/>
-    </x:row>
-    <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A17" s="10"/>
-      <x:c r="B17" s="10"/>
-      <x:c r="C17" s="10"/>
-      <x:c r="D17" s="9"/>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="10"/>
-      <x:c r="H17" s="10"/>
-    </x:row>
-    <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A18" s="10"/>
-      <x:c r="B18" s="10"/>
-      <x:c r="C18" s="10"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10"/>
-      <x:c r="H18" s="10"/>
-    </x:row>
-    <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A19" s="10"/>
-      <x:c r="B19" s="10"/>
-      <x:c r="C19" s="10"/>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="G19" s="10"/>
-      <x:c r="H19" s="10"/>
-    </x:row>
-    <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A20" s="10"/>
-      <x:c r="B20" s="10"/>
-      <x:c r="C20" s="10"/>
-      <x:c r="D20" s="9"/>
-      <x:c r="E20" s="9"/>
-      <x:c r="F20" s="9"/>
-      <x:c r="G20" s="10"/>
-      <x:c r="H20" s="10"/>
-    </x:row>
-    <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A21" s="10"/>
-      <x:c r="B21" s="10"/>
-      <x:c r="C21" s="10"/>
-      <x:c r="D21" s="9"/>
-      <x:c r="E21" s="9"/>
-      <x:c r="F21" s="9"/>
-      <x:c r="G21" s="10"/>
-      <x:c r="H21" s="10"/>
-    </x:row>
-    <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A22" s="10"/>
-      <x:c r="B22" s="10"/>
-      <x:c r="C22" s="10"/>
-      <x:c r="D22" s="9"/>
-      <x:c r="E22" s="9"/>
-      <x:c r="F22" s="9"/>
-      <x:c r="G22" s="10"/>
-      <x:c r="H22" s="10"/>
-    </x:row>
-    <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A23" s="10"/>
-      <x:c r="B23" s="10"/>
-      <x:c r="C23" s="10"/>
-      <x:c r="D23" s="9"/>
-      <x:c r="E23" s="9"/>
-      <x:c r="F23" s="9"/>
-      <x:c r="G23" s="10"/>
-      <x:c r="H23" s="10"/>
-    </x:row>
-    <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A24" s="10"/>
-      <x:c r="B24" s="10"/>
-      <x:c r="C24" s="10"/>
-      <x:c r="D24" s="9"/>
-      <x:c r="E24" s="9"/>
-      <x:c r="F24" s="9"/>
-      <x:c r="G24" s="10"/>
-      <x:c r="H24" s="10"/>
-    </x:row>
-    <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A25" s="10"/>
-      <x:c r="B25" s="10"/>
-      <x:c r="C25" s="10"/>
-      <x:c r="D25" s="9"/>
-      <x:c r="E25" s="9"/>
-      <x:c r="F25" s="9"/>
-      <x:c r="G25" s="10"/>
-      <x:c r="H25" s="10"/>
-    </x:row>
-    <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="11"/>
-      <x:c r="D26" s="11"/>
-      <x:c r="E26" s="11"/>
-      <x:c r="F26" s="11"/>
-      <x:c r="G26" s="11"/>
-      <x:c r="H26" s="11"/>
-    </x:row>
-    <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="11"/>
-      <x:c r="D27" s="11"/>
-      <x:c r="E27" s="11"/>
-      <x:c r="F27" s="11"/>
-      <x:c r="G27" s="11"/>
-      <x:c r="H27" s="11"/>
-    </x:row>
-    <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="11"/>
-      <x:c r="D28" s="11"/>
-      <x:c r="E28" s="11"/>
-      <x:c r="F28" s="11"/>
-      <x:c r="G28" s="11"/>
-      <x:c r="H28" s="11"/>
-    </x:row>
-    <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="11"/>
-      <x:c r="D29" s="11"/>
-      <x:c r="E29" s="11"/>
-      <x:c r="F29" s="11"/>
-      <x:c r="G29" s="11"/>
-      <x:c r="H29" s="11"/>
-    </x:row>
-    <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="11"/>
-      <x:c r="D30" s="11"/>
-      <x:c r="E30" s="11"/>
-      <x:c r="F30" s="11"/>
-      <x:c r="G30" s="11"/>
-      <x:c r="H30" s="11"/>
-    </x:row>
-    <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="11"/>
-      <x:c r="D31" s="11"/>
-      <x:c r="E31" s="11"/>
-      <x:c r="F31" s="11"/>
-      <x:c r="G31" s="11"/>
-      <x:c r="H31" s="11"/>
-    </x:row>
-    <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A32" s="12"/>
-      <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
-      <x:c r="D32" s="12"/>
-      <x:c r="E32" s="12"/>
-      <x:c r="F32" s="12"/>
-      <x:c r="G32" s="12"/>
-      <x:c r="H32" s="12"/>
-    </x:row>
-    <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A33" s="12"/>
-      <x:c r="B33" s="12"/>
-      <x:c r="C33" s="12"/>
-      <x:c r="D33" s="12"/>
-      <x:c r="E33" s="12"/>
-      <x:c r="F33" s="12"/>
-      <x:c r="G33" s="12"/>
-      <x:c r="H33" s="12"/>
-    </x:row>
-    <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A34" s="12"/>
-      <x:c r="B34" s="12"/>
-      <x:c r="C34" s="12"/>
-      <x:c r="D34" s="12"/>
-      <x:c r="E34" s="12"/>
-      <x:c r="F34" s="12"/>
-      <x:c r="G34" s="12"/>
-      <x:c r="H34" s="12"/>
-    </x:row>
-    <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A35" s="12"/>
-      <x:c r="B35" s="12"/>
-      <x:c r="C35" s="12"/>
-      <x:c r="D35" s="12"/>
-      <x:c r="E35" s="12"/>
-      <x:c r="F35" s="12"/>
-      <x:c r="G35" s="12"/>
-      <x:c r="H35" s="12"/>
+      <x:c r="B16" s="3"/>
+      <x:c r="C16" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D16" s="3"/>
+      <x:c r="E16" s="3"/>
+      <x:c r="F16" s="3"/>
+      <x:c r="G16" s="3"/>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="7"/>
+      <x:c r="J16" s="7"/>
+      <x:c r="K16" s="7"/>
+      <x:c r="L16" s="7"/>
+      <x:c r="M16" s="7"/>
+      <x:c r="N16" s="7"/>
+      <x:c r="O16" s="7"/>
+      <x:c r="P16" s="7"/>
+      <x:c r="Q16" s="7"/>
+      <x:c r="R16" s="7"/>
+      <x:c r="S16" s="7"/>
+      <x:c r="T16" s="7"/>
+      <x:c r="U16" s="7"/>
+      <x:c r="V16" s="7"/>
+    </x:row>
+    <x:row r="17" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A17" s="3"/>
+      <x:c r="B17" s="3"/>
+      <x:c r="C17" s="3"/>
+      <x:c r="D17" s="3"/>
+      <x:c r="E17" s="3"/>
+      <x:c r="F17" s="3"/>
+      <x:c r="G17" s="3"/>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="7"/>
+      <x:c r="J17" s="7"/>
+      <x:c r="K17" s="7"/>
+      <x:c r="L17" s="7"/>
+      <x:c r="M17" s="7"/>
+      <x:c r="N17" s="7"/>
+      <x:c r="O17" s="7"/>
+      <x:c r="P17" s="7"/>
+      <x:c r="Q17" s="7"/>
+      <x:c r="R17" s="7"/>
+      <x:c r="S17" s="7"/>
+      <x:c r="T17" s="7"/>
+      <x:c r="U17" s="7"/>
+      <x:c r="V17" s="7"/>
+    </x:row>
+    <x:row r="18" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A18" s="3"/>
+      <x:c r="B18" s="3"/>
+      <x:c r="C18" s="3"/>
+      <x:c r="D18" s="3"/>
+      <x:c r="E18" s="3"/>
+      <x:c r="F18" s="3"/>
+      <x:c r="G18" s="3"/>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="7"/>
+      <x:c r="J18" s="7"/>
+      <x:c r="K18" s="7"/>
+      <x:c r="L18" s="7"/>
+      <x:c r="M18" s="7"/>
+      <x:c r="N18" s="7"/>
+      <x:c r="O18" s="7"/>
+      <x:c r="P18" s="7"/>
+      <x:c r="Q18" s="7"/>
+      <x:c r="R18" s="7"/>
+      <x:c r="S18" s="7"/>
+      <x:c r="T18" s="7"/>
+      <x:c r="U18" s="7"/>
+      <x:c r="V18" s="7"/>
+    </x:row>
+    <x:row r="19" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A19" s="3"/>
+      <x:c r="B19" s="3"/>
+      <x:c r="C19" s="3"/>
+      <x:c r="D19" s="3"/>
+      <x:c r="E19" s="3"/>
+      <x:c r="F19" s="3"/>
+      <x:c r="G19" s="3"/>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="7"/>
+      <x:c r="J19" s="7"/>
+      <x:c r="K19" s="7"/>
+      <x:c r="L19" s="7"/>
+      <x:c r="M19" s="7"/>
+      <x:c r="N19" s="7"/>
+      <x:c r="O19" s="7"/>
+      <x:c r="P19" s="7"/>
+      <x:c r="Q19" s="7"/>
+      <x:c r="R19" s="7"/>
+      <x:c r="S19" s="7"/>
+      <x:c r="T19" s="7"/>
+      <x:c r="U19" s="7"/>
+      <x:c r="V19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A20" s="3"/>
+      <x:c r="B20" s="3"/>
+      <x:c r="C20" s="3"/>
+      <x:c r="D20" s="3"/>
+      <x:c r="E20" s="3"/>
+      <x:c r="F20" s="3"/>
+      <x:c r="G20" s="3"/>
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="7"/>
+      <x:c r="J20" s="7"/>
+      <x:c r="K20" s="7"/>
+      <x:c r="L20" s="7"/>
+      <x:c r="M20" s="7"/>
+      <x:c r="N20" s="7"/>
+      <x:c r="O20" s="7"/>
+      <x:c r="P20" s="7"/>
+      <x:c r="Q20" s="7"/>
+      <x:c r="R20" s="7"/>
+      <x:c r="S20" s="7"/>
+      <x:c r="T20" s="7"/>
+      <x:c r="U20" s="7"/>
+      <x:c r="V20" s="7"/>
+    </x:row>
+    <x:row r="21" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A21" s="3"/>
+      <x:c r="B21" s="3"/>
+      <x:c r="C21" s="3"/>
+      <x:c r="D21" s="3"/>
+      <x:c r="E21" s="3"/>
+      <x:c r="F21" s="3"/>
+      <x:c r="G21" s="3"/>
+      <x:c r="H21" s="3"/>
+      <x:c r="I21" s="7"/>
+      <x:c r="J21" s="7"/>
+      <x:c r="K21" s="7"/>
+      <x:c r="L21" s="7"/>
+      <x:c r="M21" s="7"/>
+      <x:c r="N21" s="7"/>
+      <x:c r="O21" s="7"/>
+      <x:c r="P21" s="7"/>
+      <x:c r="Q21" s="7"/>
+      <x:c r="R21" s="7"/>
+      <x:c r="S21" s="7"/>
+      <x:c r="T21" s="7"/>
+      <x:c r="U21" s="7"/>
+      <x:c r="V21" s="7"/>
+    </x:row>
+    <x:row r="22" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A22" s="3"/>
+      <x:c r="B22" s="3"/>
+      <x:c r="C22" s="3"/>
+      <x:c r="D22" s="3"/>
+      <x:c r="E22" s="3"/>
+      <x:c r="F22" s="3"/>
+      <x:c r="G22" s="3"/>
+      <x:c r="H22" s="3"/>
+      <x:c r="I22" s="7"/>
+      <x:c r="J22" s="7"/>
+      <x:c r="K22" s="7"/>
+      <x:c r="L22" s="7"/>
+      <x:c r="M22" s="7"/>
+      <x:c r="N22" s="7"/>
+      <x:c r="O22" s="7"/>
+      <x:c r="P22" s="7"/>
+      <x:c r="Q22" s="7"/>
+      <x:c r="R22" s="7"/>
+      <x:c r="S22" s="7"/>
+      <x:c r="T22" s="7"/>
+      <x:c r="U22" s="7"/>
+      <x:c r="V22" s="7"/>
+    </x:row>
+    <x:row r="23" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A23" s="3"/>
+      <x:c r="B23" s="3"/>
+      <x:c r="C23" s="3"/>
+      <x:c r="D23" s="3"/>
+      <x:c r="E23" s="3"/>
+      <x:c r="F23" s="3"/>
+      <x:c r="G23" s="3"/>
+      <x:c r="H23" s="3"/>
+      <x:c r="I23" s="7"/>
+      <x:c r="J23" s="7"/>
+      <x:c r="K23" s="7"/>
+      <x:c r="L23" s="7"/>
+      <x:c r="M23" s="7"/>
+      <x:c r="N23" s="7"/>
+      <x:c r="O23" s="7"/>
+      <x:c r="P23" s="7"/>
+      <x:c r="Q23" s="7"/>
+      <x:c r="R23" s="7"/>
+      <x:c r="S23" s="7"/>
+      <x:c r="T23" s="7"/>
+      <x:c r="U23" s="7"/>
+      <x:c r="V23" s="7"/>
+    </x:row>
+    <x:row r="24" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A24" s="3"/>
+      <x:c r="B24" s="3"/>
+      <x:c r="C24" s="3"/>
+      <x:c r="D24" s="3"/>
+      <x:c r="E24" s="3"/>
+      <x:c r="F24" s="3"/>
+      <x:c r="G24" s="3"/>
+      <x:c r="H24" s="3"/>
+      <x:c r="I24" s="7"/>
+      <x:c r="J24" s="7"/>
+      <x:c r="K24" s="7"/>
+      <x:c r="L24" s="7"/>
+      <x:c r="M24" s="7"/>
+      <x:c r="N24" s="7"/>
+      <x:c r="O24" s="7"/>
+      <x:c r="P24" s="7"/>
+      <x:c r="Q24" s="7"/>
+      <x:c r="R24" s="7"/>
+      <x:c r="S24" s="7"/>
+      <x:c r="T24" s="7"/>
+      <x:c r="U24" s="7"/>
+      <x:c r="V24" s="7"/>
+    </x:row>
+    <x:row r="25" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A25" s="3"/>
+      <x:c r="B25" s="3"/>
+      <x:c r="C25" s="3"/>
+      <x:c r="D25" s="3"/>
+      <x:c r="E25" s="3"/>
+      <x:c r="F25" s="3"/>
+      <x:c r="G25" s="3"/>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="7"/>
+      <x:c r="J25" s="7"/>
+      <x:c r="K25" s="7"/>
+      <x:c r="L25" s="7"/>
+      <x:c r="M25" s="7"/>
+      <x:c r="N25" s="7"/>
+      <x:c r="O25" s="7"/>
+      <x:c r="P25" s="7"/>
+      <x:c r="Q25" s="7"/>
+      <x:c r="R25" s="7"/>
+      <x:c r="S25" s="7"/>
+      <x:c r="T25" s="7"/>
+      <x:c r="U25" s="7"/>
+      <x:c r="V25" s="7"/>
+    </x:row>
+    <x:row r="26" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="4"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="7"/>
+      <x:c r="J26" s="7"/>
+      <x:c r="K26" s="7"/>
+      <x:c r="L26" s="7"/>
+      <x:c r="M26" s="7"/>
+      <x:c r="N26" s="7"/>
+      <x:c r="O26" s="7"/>
+      <x:c r="P26" s="7"/>
+      <x:c r="Q26" s="7"/>
+      <x:c r="R26" s="7"/>
+      <x:c r="S26" s="7"/>
+      <x:c r="T26" s="7"/>
+      <x:c r="U26" s="7"/>
+      <x:c r="V26" s="7"/>
+    </x:row>
+    <x:row r="27" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="4"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="7"/>
+      <x:c r="J27" s="7"/>
+      <x:c r="K27" s="7"/>
+      <x:c r="L27" s="7"/>
+      <x:c r="M27" s="7"/>
+      <x:c r="N27" s="7"/>
+      <x:c r="O27" s="7"/>
+      <x:c r="P27" s="7"/>
+      <x:c r="Q27" s="7"/>
+      <x:c r="R27" s="7"/>
+      <x:c r="S27" s="7"/>
+      <x:c r="T27" s="7"/>
+      <x:c r="U27" s="7"/>
+      <x:c r="V27" s="7"/>
+    </x:row>
+    <x:row r="28" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="4"/>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="4"/>
+      <x:c r="G28" s="4"/>
+      <x:c r="H28" s="4"/>
+      <x:c r="I28" s="7"/>
+      <x:c r="J28" s="7"/>
+      <x:c r="K28" s="7"/>
+      <x:c r="L28" s="7"/>
+      <x:c r="M28" s="7"/>
+      <x:c r="N28" s="7"/>
+      <x:c r="O28" s="7"/>
+      <x:c r="P28" s="7"/>
+      <x:c r="Q28" s="7"/>
+      <x:c r="R28" s="7"/>
+      <x:c r="S28" s="7"/>
+      <x:c r="T28" s="7"/>
+      <x:c r="U28" s="7"/>
+      <x:c r="V28" s="7"/>
+    </x:row>
+    <x:row r="29" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="4"/>
+      <x:c r="I29" s="7"/>
+      <x:c r="J29" s="7"/>
+      <x:c r="K29" s="7"/>
+      <x:c r="L29" s="7"/>
+      <x:c r="M29" s="7"/>
+      <x:c r="N29" s="7"/>
+      <x:c r="O29" s="7"/>
+      <x:c r="P29" s="7"/>
+      <x:c r="Q29" s="7"/>
+      <x:c r="R29" s="7"/>
+      <x:c r="S29" s="7"/>
+      <x:c r="T29" s="7"/>
+      <x:c r="U29" s="7"/>
+      <x:c r="V29" s="7"/>
+    </x:row>
+    <x:row r="30" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="4"/>
+      <x:c r="E30" s="4"/>
+      <x:c r="F30" s="4"/>
+      <x:c r="G30" s="4"/>
+      <x:c r="H30" s="4"/>
+      <x:c r="I30" s="7"/>
+      <x:c r="J30" s="7"/>
+      <x:c r="K30" s="7"/>
+      <x:c r="L30" s="7"/>
+      <x:c r="M30" s="7"/>
+      <x:c r="N30" s="7"/>
+      <x:c r="O30" s="7"/>
+      <x:c r="P30" s="7"/>
+      <x:c r="Q30" s="7"/>
+      <x:c r="R30" s="7"/>
+      <x:c r="S30" s="7"/>
+      <x:c r="T30" s="7"/>
+      <x:c r="U30" s="7"/>
+      <x:c r="V30" s="7"/>
+    </x:row>
+    <x:row r="31" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A31" s="4"/>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="4"/>
+      <x:c r="E31" s="4"/>
+      <x:c r="F31" s="4"/>
+      <x:c r="G31" s="4"/>
+      <x:c r="H31" s="4"/>
+      <x:c r="I31" s="7"/>
+      <x:c r="J31" s="7"/>
+      <x:c r="K31" s="7"/>
+      <x:c r="L31" s="7"/>
+      <x:c r="M31" s="7"/>
+      <x:c r="N31" s="7"/>
+      <x:c r="O31" s="7"/>
+      <x:c r="P31" s="7"/>
+      <x:c r="Q31" s="7"/>
+      <x:c r="R31" s="7"/>
+      <x:c r="S31" s="7"/>
+      <x:c r="T31" s="7"/>
+      <x:c r="U31" s="7"/>
+      <x:c r="V31" s="7"/>
+    </x:row>
+    <x:row r="32" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A32" s="5"/>
+      <x:c r="B32" s="5"/>
+      <x:c r="C32" s="5"/>
+      <x:c r="D32" s="5"/>
+      <x:c r="E32" s="5"/>
+      <x:c r="F32" s="5"/>
+      <x:c r="G32" s="5"/>
+      <x:c r="H32" s="5"/>
+      <x:c r="I32" s="7"/>
+      <x:c r="J32" s="7"/>
+      <x:c r="K32" s="7"/>
+      <x:c r="L32" s="7"/>
+      <x:c r="M32" s="7"/>
+      <x:c r="N32" s="7"/>
+      <x:c r="O32" s="7"/>
+      <x:c r="P32" s="7"/>
+      <x:c r="Q32" s="7"/>
+      <x:c r="R32" s="7"/>
+      <x:c r="S32" s="7"/>
+      <x:c r="T32" s="7"/>
+      <x:c r="U32" s="7"/>
+      <x:c r="V32" s="7"/>
+    </x:row>
+    <x:row r="33" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A33" s="5"/>
+      <x:c r="B33" s="5"/>
+      <x:c r="C33" s="5"/>
+      <x:c r="D33" s="5"/>
+      <x:c r="E33" s="5"/>
+      <x:c r="F33" s="5"/>
+      <x:c r="G33" s="5"/>
+      <x:c r="H33" s="5"/>
+      <x:c r="I33" s="7"/>
+      <x:c r="J33" s="7"/>
+      <x:c r="K33" s="7"/>
+      <x:c r="L33" s="7"/>
+      <x:c r="M33" s="7"/>
+      <x:c r="N33" s="7"/>
+      <x:c r="O33" s="7"/>
+      <x:c r="P33" s="7"/>
+      <x:c r="Q33" s="7"/>
+      <x:c r="R33" s="7"/>
+      <x:c r="S33" s="7"/>
+      <x:c r="T33" s="7"/>
+      <x:c r="U33" s="7"/>
+      <x:c r="V33" s="7"/>
+    </x:row>
+    <x:row r="34" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A34" s="5"/>
+      <x:c r="B34" s="5"/>
+      <x:c r="C34" s="5"/>
+      <x:c r="D34" s="5"/>
+      <x:c r="E34" s="5"/>
+      <x:c r="F34" s="5"/>
+      <x:c r="G34" s="5"/>
+      <x:c r="H34" s="5"/>
+      <x:c r="I34" s="7"/>
+      <x:c r="J34" s="7"/>
+      <x:c r="K34" s="7"/>
+      <x:c r="L34" s="7"/>
+      <x:c r="M34" s="7"/>
+      <x:c r="N34" s="7"/>
+      <x:c r="O34" s="7"/>
+      <x:c r="P34" s="7"/>
+      <x:c r="Q34" s="7"/>
+      <x:c r="R34" s="7"/>
+      <x:c r="S34" s="7"/>
+      <x:c r="T34" s="7"/>
+      <x:c r="U34" s="7"/>
+      <x:c r="V34" s="7"/>
+    </x:row>
+    <x:row r="35" spans="1:22" ht="15.75" customHeight="1">
+      <x:c r="A35" s="5"/>
+      <x:c r="B35" s="5"/>
+      <x:c r="C35" s="5"/>
+      <x:c r="D35" s="5"/>
+      <x:c r="E35" s="5"/>
+      <x:c r="F35" s="5"/>
+      <x:c r="G35" s="5"/>
+      <x:c r="H35" s="5"/>
+      <x:c r="I35" s="7"/>
+      <x:c r="J35" s="7"/>
+      <x:c r="K35" s="7"/>
+      <x:c r="L35" s="7"/>
+      <x:c r="M35" s="7"/>
+      <x:c r="N35" s="7"/>
+      <x:c r="O35" s="7"/>
+      <x:c r="P35" s="7"/>
+      <x:c r="Q35" s="7"/>
+      <x:c r="R35" s="7"/>
+      <x:c r="S35" s="7"/>
+      <x:c r="T35" s="7"/>
+      <x:c r="U35" s="7"/>
+      <x:c r="V35" s="7"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -21,133 +21,133 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <x:si>
+    <x:t>dialogue_group_mainstream_1_2_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거대한 뱀이 공격해온다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제의 세계에 접속했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분명 처음 보는 풍경인데</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여긴 어디지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_ellie_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 대답하지 않는다,대답한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭔가 한달 내내 본것같은 지긋지긋한 느낌이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_enterbattle_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 쓰러트렸으니 돌아갈 수 있을것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>한달 묵은것치곤 많이 허술한 뱀이였다..</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_clearbattle_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_clearbattle_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Texture2D_Loading_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여긴 어디지...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 대답하지 않는다,대답한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_ellie_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_enterbattle_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭔가 한달 내내 본것같은 지긋지긋한 느낌이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거대한 뱀이 공격해온다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제의 세계에 접속했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분명 처음 보는 풍경인데</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 쓰러트렸으니 돌아갈 수 있을것 같다.</x:t>
+    <x:t>SelectionDialogueIdList</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainstory_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstory_1_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstory_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -919,7 +919,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -945,28 +945,28 @@
     </x:row>
     <x:row r="2" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A2" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H2" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="7"/>
       <x:c r="J2" s="7"/>
@@ -985,28 +985,28 @@
     </x:row>
     <x:row r="3" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A3" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C3" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D3" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G3" s="8" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H3" s="8" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="7"/>
       <x:c r="J3" s="7"/>
@@ -1025,19 +1025,19 @@
     </x:row>
     <x:row r="4" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A4" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="10"/>
       <x:c r="C4" s="9" t="s">
-        <x:v>33</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="9" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="9" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H4" s="9"/>
       <x:c r="I4" s="2"/>
@@ -1057,14 +1057,14 @@
     </x:row>
     <x:row r="5" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A5" s="9" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="10"/>
       <x:c r="C5" s="9" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D5" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E5" s="9"/>
       <x:c r="F5" s="9"/>
@@ -1087,18 +1087,18 @@
     </x:row>
     <x:row r="6" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A6" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="10"/>
       <x:c r="C6" s="9" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="9"/>
       <x:c r="E6" s="9"/>
       <x:c r="F6" s="9"/>
       <x:c r="G6" s="9"/>
       <x:c r="H6" s="9" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="2"/>
@@ -1117,18 +1117,18 @@
     </x:row>
     <x:row r="7" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A7" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="9"/>
       <x:c r="C7" s="9" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="9" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="9"/>
       <x:c r="H7" s="9"/>
@@ -1149,11 +1149,11 @@
     </x:row>
     <x:row r="8" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A8" s="9" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="11"/>
       <x:c r="E8" s="11"/>
@@ -1177,18 +1177,18 @@
     </x:row>
     <x:row r="9" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A9" s="9" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="11"/>
       <x:c r="E9" s="11"/>
       <x:c r="F9" s="11"/>
       <x:c r="G9" s="11"/>
       <x:c r="H9" s="9" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>
@@ -1207,11 +1207,11 @@
     </x:row>
     <x:row r="10" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A10" s="9" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="12"/>
       <x:c r="C10" s="12" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="12"/>
       <x:c r="E10" s="12"/>
@@ -1235,16 +1235,16 @@
     </x:row>
     <x:row r="11" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -1267,16 +1267,16 @@
     </x:row>
     <x:row r="12" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="11" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D12" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E12" s="11"/>
       <x:c r="F12" s="11"/>
@@ -1299,10 +1299,10 @@
     </x:row>
     <x:row r="13" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
         <x:v>31</x:v>
@@ -1329,11 +1329,11 @@
     </x:row>
     <x:row r="14" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="12"/>
       <x:c r="C14" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D14" s="12"/>
       <x:c r="E14" s="12"/>
@@ -1357,14 +1357,14 @@
     </x:row>
     <x:row r="15" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A15" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="12"/>
       <x:c r="C15" s="12" t="s">
-        <x:v>0</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="12"/>
       <x:c r="F15" s="12"/>
@@ -1387,11 +1387,11 @@
     </x:row>
     <x:row r="16" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A16" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="3"/>
       <x:c r="C16" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D16" s="3"/>
       <x:c r="E16" s="3"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -19,7 +19,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>커피인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피자인가..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뱀 다음은 용이라니!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여긴 어디지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 대답하지 않는다,대답한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_ellie_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
+  </x:si>
   <x:si>
     <x:t>dialogue_group_mainstream_1_2_100</x:t>
   </x:si>
@@ -30,16 +75,73 @@
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
+    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 진짜 끝인건가..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_enterbattle_2_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_enterbattle_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뭔가 한달 내내 본것같은 지긋지긋한 느낌이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_2_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_2_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 해치운것같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주위를 살펴보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
   </x:si>
   <x:si>
     <x:t>거대한 뱀이 공격해온다!</x:t>
   </x:si>
   <x:si>
-    <x:t>CharacterDataId</x:t>
+    <x:t>NextDialogueId</x:t>
   </x:si>
   <x:si>
     <x:t>과제의 세계에 접속했습니다</x:t>
@@ -48,103 +150,19 @@
     <x:t>분명 처음 보는 풍경인데</x:t>
   </x:si>
   <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여긴 어디지...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_ellie_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 대답하지 않는다,대답한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Texture2D_Loading_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_clearbattle_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_clearbattle_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뭔가 한달 내내 본것같은 지긋지긋한 느낌이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_enterbattle_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 쓰러트렸으니 돌아갈 수 있을것 같다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_mainstory_1_3</x:t>
   </x:si>
   <x:si>
+    <x:t>한달 묵은것치곤 많이 허술한 뱀이였다..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
     <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainstory_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한달 묵은것치곤 많이 허술한 뱀이였다..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainstory_1_1</x:t>
@@ -919,7 +937,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -945,28 +963,28 @@
     </x:row>
     <x:row r="2" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A2" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H2" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I2" s="7"/>
       <x:c r="J2" s="7"/>
@@ -985,28 +1003,28 @@
     </x:row>
     <x:row r="3" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A3" s="8" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G3" s="8" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="H3" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I3" s="7"/>
       <x:c r="J3" s="7"/>
@@ -1025,19 +1043,19 @@
     </x:row>
     <x:row r="4" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A4" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="10"/>
       <x:c r="C4" s="9" t="s">
-        <x:v>7</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="9" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H4" s="9"/>
       <x:c r="I4" s="2"/>
@@ -1057,14 +1075,14 @@
     </x:row>
     <x:row r="5" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A5" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="10"/>
       <x:c r="C5" s="9" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E5" s="9"/>
       <x:c r="F5" s="9"/>
@@ -1087,18 +1105,18 @@
     </x:row>
     <x:row r="6" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A6" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="10"/>
       <x:c r="C6" s="9" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="9"/>
       <x:c r="E6" s="9"/>
       <x:c r="F6" s="9"/>
       <x:c r="G6" s="9"/>
       <x:c r="H6" s="9" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="2"/>
@@ -1117,18 +1135,18 @@
     </x:row>
     <x:row r="7" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A7" s="9" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="9"/>
       <x:c r="C7" s="9" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="9" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="9"/>
       <x:c r="H7" s="9"/>
@@ -1149,11 +1167,11 @@
     </x:row>
     <x:row r="8" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A8" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="11"/>
       <x:c r="E8" s="11"/>
@@ -1177,18 +1195,18 @@
     </x:row>
     <x:row r="9" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A9" s="9" t="s">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="11"/>
       <x:c r="E9" s="11"/>
       <x:c r="F9" s="11"/>
       <x:c r="G9" s="11"/>
       <x:c r="H9" s="9" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>
@@ -1207,11 +1225,11 @@
     </x:row>
     <x:row r="10" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A10" s="9" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B10" s="12"/>
       <x:c r="C10" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="12"/>
       <x:c r="E10" s="12"/>
@@ -1235,16 +1253,16 @@
     </x:row>
     <x:row r="11" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C11" s="12" t="s">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -1267,16 +1285,16 @@
     </x:row>
     <x:row r="12" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E12" s="11"/>
       <x:c r="F12" s="11"/>
@@ -1299,13 +1317,13 @@
     </x:row>
     <x:row r="13" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
@@ -1329,11 +1347,11 @@
     </x:row>
     <x:row r="14" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B14" s="12"/>
       <x:c r="C14" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D14" s="12"/>
       <x:c r="E14" s="12"/>
@@ -1357,11 +1375,11 @@
     </x:row>
     <x:row r="15" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A15" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="12"/>
       <x:c r="C15" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
         <x:v>29</x:v>
@@ -1414,9 +1432,13 @@
       <x:c r="V16" s="7"/>
     </x:row>
     <x:row r="17" spans="1:22" ht="15.75" customHeight="1">
-      <x:c r="A17" s="3"/>
+      <x:c r="A17" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="B17" s="3"/>
-      <x:c r="C17" s="3"/>
+      <x:c r="C17" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="D17" s="3"/>
       <x:c r="E17" s="3"/>
       <x:c r="F17" s="3"/>
@@ -1438,10 +1460,16 @@
       <x:c r="V17" s="7"/>
     </x:row>
     <x:row r="18" spans="1:22" ht="15.75" customHeight="1">
-      <x:c r="A18" s="3"/>
+      <x:c r="A18" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
       <x:c r="B18" s="3"/>
-      <x:c r="C18" s="3"/>
-      <x:c r="D18" s="3"/>
+      <x:c r="C18" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="E18" s="3"/>
       <x:c r="F18" s="3"/>
       <x:c r="G18" s="3"/>
@@ -1462,9 +1490,13 @@
       <x:c r="V18" s="7"/>
     </x:row>
     <x:row r="19" spans="1:22" ht="15.75" customHeight="1">
-      <x:c r="A19" s="3"/>
+      <x:c r="A19" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="B19" s="3"/>
-      <x:c r="C19" s="3"/>
+      <x:c r="C19" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="D19" s="3"/>
       <x:c r="E19" s="3"/>
       <x:c r="F19" s="3"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="26190" windowHeight="11490"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -21,151 +21,151 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>커피인가..</x:t>
   </x:si>
   <x:si>
     <x:t>피자인가..</x:t>
   </x:si>
   <x:si>
+    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>character_ellie_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무 대답하지 않는다,대답한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제의 세계에 접속했습니다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분명 처음 보는 풍경인데</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거대한 뱀이 공격해온다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 진짜 끝인건가..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한달 묵은것치곤 많이 허술한 뱀이였다..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstory_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여긴 어디지...?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
     <x:t>뱀 다음은 용이라니!</x:t>
   </x:si>
   <x:si>
-    <x:t>여긴 어디지...?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
     <x:t>VoicePath</x:t>
   </x:si>
   <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 대답하지 않는다,대답한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_ellie_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
+    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainstream_1_2_300</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_mainstream_1_2_400</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_group_mainstream_1_2_100</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_group_mainstream_1_2_200</x:t>
   </x:si>
   <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 진짜 끝인건가..?</x:t>
+    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
   </x:si>
   <x:si>
     <x:t>Texture2D/Texture2D_Loading_1</x:t>
   </x:si>
   <x:si>
-    <x:t>사과를 10개 획득하면 클리어하게 만들고 싶었습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>주위를 살펴보자.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일단 해치운것같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_enterbattle_1_1</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_enterbattle_2_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_enterbattle_1_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>dialogue_clearbattle_1_1</x:t>
   </x:si>
   <x:si>
+    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_clearbattle_1_2</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_mainstream_1_1_200</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_clearbattle_1_2</x:t>
+    <x:t>dialogue_clearbattle_2_2</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainstream_1_1_300</x:t>
   </x:si>
   <x:si>
-    <x:t>하지만 뜻대로 작동하게 만드는게 쉽지 않네요..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
     <x:t>뭔가 한달 내내 본것같은 지긋지긋한 느낌이다.</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_clearbattle_2_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_clearbattle_2_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 해치운것같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주위를 살펴보자.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거대한 뱀이 공격해온다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제의 세계에 접속했습니다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분명 처음 보는 풍경인데</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstory_1_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한달 묵은것치곤 많이 허술한 뱀이였다..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstory_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstory_1_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -937,7 +937,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A1" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -963,28 +963,28 @@
     </x:row>
     <x:row r="2" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A2" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D2" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E2" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F2" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G2" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H2" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="7"/>
       <x:c r="J2" s="7"/>
@@ -1003,28 +1003,28 @@
     </x:row>
     <x:row r="3" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A3" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="8" t="s">
-        <x:v>38</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="8" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G3" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H3" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I3" s="7"/>
       <x:c r="J3" s="7"/>
@@ -1043,19 +1043,19 @@
     </x:row>
     <x:row r="4" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A4" s="9" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B4" s="10"/>
       <x:c r="C4" s="9" t="s">
-        <x:v>41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
       <x:c r="G4" s="9" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H4" s="9"/>
       <x:c r="I4" s="2"/>
@@ -1075,14 +1075,14 @@
     </x:row>
     <x:row r="5" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A5" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="10"/>
       <x:c r="C5" s="9" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E5" s="9"/>
       <x:c r="F5" s="9"/>
@@ -1105,18 +1105,18 @@
     </x:row>
     <x:row r="6" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A6" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="10"/>
       <x:c r="C6" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="9"/>
       <x:c r="E6" s="9"/>
       <x:c r="F6" s="9"/>
       <x:c r="G6" s="9"/>
       <x:c r="H6" s="9" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="2"/>
@@ -1135,18 +1135,18 @@
     </x:row>
     <x:row r="7" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A7" s="9" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="9"/>
       <x:c r="C7" s="9" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="9" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="9"/>
       <x:c r="H7" s="9"/>
@@ -1167,11 +1167,11 @@
     </x:row>
     <x:row r="8" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A8" s="9" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="11"/>
       <x:c r="E8" s="11"/>
@@ -1195,18 +1195,18 @@
     </x:row>
     <x:row r="9" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A9" s="9" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="11"/>
       <x:c r="E9" s="11"/>
       <x:c r="F9" s="11"/>
       <x:c r="G9" s="11"/>
       <x:c r="H9" s="9" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>
@@ -1225,11 +1225,11 @@
     </x:row>
     <x:row r="10" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A10" s="9" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="12"/>
       <x:c r="C10" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="12"/>
       <x:c r="E10" s="12"/>
@@ -1253,16 +1253,16 @@
     </x:row>
     <x:row r="11" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -1285,16 +1285,16 @@
     </x:row>
     <x:row r="12" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="11"/>
       <x:c r="F12" s="11"/>
@@ -1317,13 +1317,13 @@
     </x:row>
     <x:row r="13" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
@@ -1347,11 +1347,11 @@
     </x:row>
     <x:row r="14" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="12"/>
       <x:c r="C14" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D14" s="12"/>
       <x:c r="E14" s="12"/>
@@ -1375,14 +1375,14 @@
     </x:row>
     <x:row r="15" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A15" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="12"/>
       <x:c r="C15" s="12" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D15" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E15" s="12"/>
       <x:c r="F15" s="12"/>
@@ -1405,11 +1405,11 @@
     </x:row>
     <x:row r="16" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A16" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="3"/>
       <x:c r="C16" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="3"/>
       <x:c r="E16" s="3"/>
@@ -1433,11 +1433,11 @@
     </x:row>
     <x:row r="17" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A17" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="3"/>
       <x:c r="C17" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D17" s="3"/>
       <x:c r="E17" s="3"/>
@@ -1461,14 +1461,14 @@
     </x:row>
     <x:row r="18" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A18" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="3"/>
       <x:c r="C18" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E18" s="3"/>
       <x:c r="F18" s="3"/>
@@ -1491,11 +1491,11 @@
     </x:row>
     <x:row r="19" spans="1:22" ht="15.75" customHeight="1">
       <x:c r="A19" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="3"/>
       <x:c r="C19" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D19" s="3"/>
       <x:c r="E19" s="3"/>
